--- a/artifacts/api-server/qa-output/Single-Year_Pro_Forma_Microschool_With_Decisions.xlsx
+++ b/artifacts/api-server/qa-output/Single-Year_Pro_Forma_Microschool_With_Decisions.xlsx
@@ -9,6 +9,7 @@
     <sheet sheetId="3" name="Personnel" state="visible" r:id="rId6"/>
     <sheet sheetId="4" name="Operating Expenses" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="P&amp;L Summary" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Decision History" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Assumptions'!$A1:$E11</definedName>
@@ -21,13 +22,15 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Operating Expenses'!$1:$1</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'P&amp;L Summary'!$A1:$N7</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'P&amp;L Summary'!$1:$1</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Decision History'!$A1:$H11</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Decision History'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="88">
   <si>
     <t>Year 1 Budget Assumptions</t>
   </si>
@@ -174,6 +177,132 @@
   </si>
   <si>
     <t>Profit / (Loss)</t>
+  </si>
+  <si>
+    <t>Decision History</t>
+  </si>
+  <si>
+    <t>Track record of 5 tracked decisions (2 pursued, 1 on hold, 2 declined). Each entry shows the modeled change, the outcome the team logged, and any retrospective notes captured after the fact.</t>
+  </si>
+  <si>
+    <t>Decision</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Outcome</t>
+  </si>
+  <si>
+    <t>Applied to base model?</t>
+  </si>
+  <si>
+    <t>Outcome logged</t>
+  </si>
+  <si>
+    <t>Modeled change</t>
+  </si>
+  <si>
+    <t>What happened (retrospective)</t>
+  </si>
+  <si>
+    <t>Add Middle School program</t>
+  </si>
+  <si>
+    <t>Add a program</t>
+  </si>
+  <si>
+    <t>Pursued</t>
+  </si>
+  <si>
+    <t>[APPLIED] Folded into the base model on Apr 12, 2025</t>
+  </si>
+  <si>
+    <t>Apr 10, 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Program: Middle School (6-8)
+• Tuition $14,000/yr
+• Adds 72 cumulative students (5 yrs)
+• +2 FTE</t>
+  </si>
+  <si>
+    <t>Launched in fall 2025; enrollment hit plan within 1 student.</t>
+  </si>
+  <si>
+    <t>Increase retention focus</t>
+  </si>
+  <si>
+    <t>Change enrollment</t>
+  </si>
+  <si>
+    <t>[PENDING] Pending apply to base model</t>
+  </si>
+  <si>
+    <t>Mar 5, 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Enrollment +14 cumulative
+• Retention 92%</t>
+  </si>
+  <si>
+    <t>Retention initiatives approved; planner will reflect after Q2 board review.</t>
+  </si>
+  <si>
+    <t>Evaluate downtown campus</t>
+  </si>
+  <si>
+    <t>Evaluate a site</t>
+  </si>
+  <si>
+    <t>On hold</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>Mar 25, 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Rent $8,500/mo
+• Rent escalation 4%
+• Sqft +1500
+• Fit-out $75,000 (Y1)</t>
+  </si>
+  <si>
+    <t>Landlord negotiations paused while waiting on city zoning ruling.</t>
+  </si>
+  <si>
+    <t>Reduce K cohort</t>
+  </si>
+  <si>
+    <t>Declined</t>
+  </si>
+  <si>
+    <t>Mar 15, 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Enrollment -8 cumulative
+• Tuition $-500/student</t>
+  </si>
+  <si>
+    <t>Board declined; enrollment goals retained as originally modeled.</t>
+  </si>
+  <si>
+    <t>Move to larger building</t>
+  </si>
+  <si>
+    <t>Feb 10, 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Rent $12,000/mo
+• Sqft +4000</t>
+  </si>
+  <si>
+    <t>Costs out of reach; revisited next year after capital campaign.</t>
+  </si>
+  <si>
+    <t>Generated by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
 </sst>
 </file>
@@ -185,7 +314,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* (#,##0);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -225,8 +354,20 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="FF1E293B"/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -256,6 +397,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE8F5E9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF8E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4EC"/>
       </patternFill>
     </fill>
   </fills>
@@ -319,7 +470,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -338,6 +489,35 @@
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2168,4 +2348,214 @@
     <oddFooter>&amp;L&amp;8Built by SchoolStack Budget  •  budget.schoolstack.ai&amp;C&amp;8Page &amp;P of &amp;N&amp;R&amp;8&amp;D</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF328555"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+    </row>
+    <row r="2" ht="44" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+    </row>
+    <row r="4" ht="28" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="H4" s="18" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="19"/>
+      <c r="B5" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="G5" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="H5" s="21" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="19"/>
+      <c r="B6" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="24"/>
+      <c r="B7" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="26"/>
+      <c r="B8" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="26"/>
+      <c r="B9" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>79</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="F9" s="23" t="s">
+        <v>84</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B11" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B11:H11"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;10&amp;BBright Horizons Microschool&amp;R&amp;8&amp;IDecision History</oddHeader>
+    <oddFooter>&amp;L&amp;8Built by SchoolStack Budget  •  budget.schoolstack.ai&amp;C&amp;8Page &amp;P of &amp;N&amp;R&amp;8&amp;D</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/artifacts/api-server/qa-output/Single-Year_Pro_Forma_Microschool_With_Decisions.xlsx
+++ b/artifacts/api-server/qa-output/Single-Year_Pro_Forma_Microschool_With_Decisions.xlsx
@@ -283,7 +283,7 @@
   </si>
   <si>
     <t xml:space="preserve">• Enrollment -8 cumulative
-• Tuition $-500/student</t>
+• Tuition -$500/student</t>
   </si>
   <si>
     <t>Board declined; enrollment goals retained as originally modeled.</t>
